--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\45087114\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49371FEA-B14C-4038-A9AA-E3AAD8ACEE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA8582D-FEC9-4741-9395-A0CB9BFC6B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16080" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Documento</t>
   </si>
@@ -126,6 +125,9 @@
   </si>
   <si>
     <t>Yulieth Valentina Ruiz Guzmán</t>
+  </si>
+  <si>
+    <t>Leidy Andrea Lopez</t>
   </si>
 </sst>
 </file>
@@ -632,14 +634,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -647,7 +649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1069832679</v>
       </c>
@@ -655,7 +657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1110538315</v>
       </c>
@@ -663,7 +665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1024591972</v>
       </c>
@@ -671,7 +673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1007719161</v>
       </c>
@@ -679,7 +681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>52848062</v>
       </c>
@@ -687,7 +689,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>1000330126</v>
       </c>
@@ -695,7 +697,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>1022415180</v>
       </c>
@@ -703,7 +705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>1007437362</v>
       </c>
@@ -711,7 +713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>52360965</v>
       </c>
@@ -719,7 +721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>52359520</v>
       </c>
@@ -727,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>1024566336</v>
       </c>
@@ -735,7 +737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>1033685058</v>
       </c>
@@ -743,7 +745,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>1043663400</v>
       </c>
@@ -751,7 +753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>1021393204</v>
       </c>
@@ -759,7 +761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>1006438514</v>
       </c>
@@ -767,7 +769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>1064556081</v>
       </c>
@@ -775,7 +777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>1024574799</v>
       </c>
@@ -783,7 +785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>1023866590</v>
       </c>
@@ -791,7 +793,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>1069750848</v>
       </c>
@@ -799,7 +801,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>52937353</v>
       </c>
@@ -807,7 +809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>33223712</v>
       </c>
@@ -815,7 +817,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>1006854586</v>
       </c>
@@ -823,7 +825,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>1010207469</v>
       </c>
@@ -831,7 +833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>1030678228</v>
       </c>
@@ -839,7 +841,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>52542666</v>
       </c>
@@ -847,7 +849,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>1032677600</v>
       </c>
@@ -855,7 +857,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1000784663</v>
       </c>
@@ -863,12 +865,20 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1006126137</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>1010231249</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -876,9 +886,9 @@
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
     <cfRule type="duplicateValues" dxfId="4" priority="6"/>
     <cfRule type="duplicateValues" dxfId="3" priority="7"/>
     <cfRule type="duplicateValues" dxfId="2" priority="8"/>
@@ -886,7 +896,7 @@
   <conditionalFormatting sqref="A20:A21">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A22:A29">
+  <conditionalFormatting sqref="A22:A30">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA8582D-FEC9-4741-9395-A0CB9BFC6B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46952B2E-8DCB-954F-864D-F0038FCC538C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16080" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Documento</t>
   </si>
@@ -55,12 +55,6 @@
     <t>Isabela Estefania Bernal Molina</t>
   </si>
   <si>
-    <t xml:space="preserve">Cecilia Perilla Rojas </t>
-  </si>
-  <si>
-    <t>Jeimy Alejandra Castillo Colorado</t>
-  </si>
-  <si>
     <t>Luisa Fernanda Palma Gonzalez</t>
   </si>
   <si>
@@ -73,21 +67,12 @@
     <t xml:space="preserve">Daira Yamileth Florez Muñoz </t>
   </si>
   <si>
-    <t xml:space="preserve">Maria Paula Olarte Rivera </t>
-  </si>
-  <si>
     <t>Johan Esteban Acosta Martinez</t>
   </si>
   <si>
     <t>Tommy Luis Pajaro gomez</t>
   </si>
   <si>
-    <t>Pablo Esteban Pedraza Alvarez</t>
-  </si>
-  <si>
-    <t>Carol Liced  Quiroga Rueda</t>
-  </si>
-  <si>
     <t>Wendy Johana Diaz Barceló</t>
   </si>
   <si>
@@ -115,9 +100,6 @@
     <t>Laura Gineeth Sánchez García</t>
   </si>
   <si>
-    <t>Carol Johanna Varón Cardona</t>
-  </si>
-  <si>
     <t>Dylan Andrés Rubiano Acevedo</t>
   </si>
   <si>
@@ -128,6 +110,57 @@
   </si>
   <si>
     <t>Leidy Andrea Lopez</t>
+  </si>
+  <si>
+    <t>Andres Cruz (Prueba)</t>
+  </si>
+  <si>
+    <t>Luisa María Restrepo Bran</t>
+  </si>
+  <si>
+    <t>Laura Inés Sánchez Velásquez</t>
+  </si>
+  <si>
+    <t>Yuli Tatiana Marin Rondon</t>
+  </si>
+  <si>
+    <t>Maidy Yineth Fernandez Fernandez</t>
+  </si>
+  <si>
+    <t>Daniel Mestre Suescun</t>
+  </si>
+  <si>
+    <t>Liliana Maria Bogota Navarro</t>
+  </si>
+  <si>
+    <t>Girlesa Eugenia Monsalve Castro</t>
+  </si>
+  <si>
+    <t>Ana María guerra Álvarez</t>
+  </si>
+  <si>
+    <t>Gustavo Adolfo Zea Valencia</t>
+  </si>
+  <si>
+    <t>Fernando Alonso García Urbaneja</t>
+  </si>
+  <si>
+    <t>Carlos Andres Mojica Betancur</t>
+  </si>
+  <si>
+    <t>Alejandro Cardona Rueda</t>
+  </si>
+  <si>
+    <t>Mildrey Cano Loaiza</t>
+  </si>
+  <si>
+    <t>Santiago Argumedo Montoya</t>
+  </si>
+  <si>
+    <t>Valeria Suárez Cuartas</t>
+  </si>
+  <si>
+    <t>Jose Andres Toro Correa</t>
   </si>
 </sst>
 </file>
@@ -213,7 +246,47 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -634,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -683,7 +756,7 @@
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>52848062</v>
+        <v>1022415180</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
@@ -691,7 +764,7 @@
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>1000330126</v>
+        <v>1007437362</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>7</v>
@@ -699,7 +772,7 @@
     </row>
     <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>1022415180</v>
+        <v>52360965</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
@@ -707,7 +780,7 @@
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>1007437362</v>
+        <v>52359520</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -715,7 +788,7 @@
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>52360965</v>
+        <v>1033685058</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -723,7 +796,7 @@
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>52359520</v>
+        <v>1043663400</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
@@ -731,7 +804,7 @@
     </row>
     <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>1024566336</v>
+        <v>1064556081</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>12</v>
@@ -739,7 +812,7 @@
     </row>
     <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>1033685058</v>
+        <v>1024574799</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>13</v>
@@ -747,7 +820,7 @@
     </row>
     <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>1043663400</v>
+        <v>1023866590</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>14</v>
@@ -755,7 +828,7 @@
     </row>
     <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>1021393204</v>
+        <v>1069750848</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>15</v>
@@ -763,7 +836,7 @@
     </row>
     <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>1006438514</v>
+        <v>52937353</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>16</v>
@@ -771,7 +844,7 @@
     </row>
     <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>1064556081</v>
+        <v>33223712</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>17</v>
@@ -779,7 +852,7 @@
     </row>
     <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>1024574799</v>
+        <v>1006854586</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>18</v>
@@ -787,7 +860,7 @@
     </row>
     <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>1023866590</v>
+        <v>1010207469</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>19</v>
@@ -795,7 +868,7 @@
     </row>
     <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>1069750848</v>
+        <v>1030678228</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>20</v>
@@ -803,7 +876,7 @@
     </row>
     <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>52937353</v>
+        <v>1032677600</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>21</v>
@@ -811,7 +884,7 @@
     </row>
     <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>33223712</v>
+        <v>1000784663</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>22</v>
@@ -819,7 +892,7 @@
     </row>
     <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>1006854586</v>
+        <v>1006126137</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>23</v>
@@ -827,7 +900,7 @@
     </row>
     <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>1010207469</v>
+        <v>1010231249</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
@@ -835,7 +908,7 @@
     </row>
     <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>1030678228</v>
+        <v>1022399552</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>25</v>
@@ -843,7 +916,7 @@
     </row>
     <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>52542666</v>
+        <v>1000873002</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>26</v>
@@ -851,7 +924,7 @@
     </row>
     <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>1032677600</v>
+        <v>1128277446</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>27</v>
@@ -859,7 +932,7 @@
     </row>
     <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>1000784663</v>
+        <v>1000635646</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>28</v>
@@ -867,7 +940,7 @@
     </row>
     <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>1006126137</v>
+        <v>1030680116</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>29</v>
@@ -875,29 +948,125 @@
     </row>
     <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>1010231249</v>
+        <v>1035230632</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>1128450311</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>43482107</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>43182389</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>1035416124</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>1096256836</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>71311840</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>1020103943</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>1007253252</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>1000406210</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>1001138890</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>1214729990</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A19">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+  <conditionalFormatting sqref="A15:A16">
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20:A21">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="A17:A41">
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A22:A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A2:A14">
+    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26:A41">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A38:B38 A36:A37">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46952B2E-8DCB-954F-864D-F0038FCC538C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000951B3-6058-C746-846C-8734C2463E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16080" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16020" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Documento</t>
   </si>
@@ -161,6 +161,18 @@
   </si>
   <si>
     <t>Jose Andres Toro Correa</t>
+  </si>
+  <si>
+    <t>Paula Andrea Martínez Neira</t>
+  </si>
+  <si>
+    <t>Javier Alejandro Angarita Prada</t>
+  </si>
+  <si>
+    <t>Juana Valeria Tibaguy Sierra</t>
+  </si>
+  <si>
+    <t>Carlos Emilio Riascos Angulo</t>
   </si>
 </sst>
 </file>
@@ -707,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -1042,25 +1054,57 @@
         <v>41</v>
       </c>
     </row>
+    <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>1010213899</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>1232399996</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>1001299432</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>1006187617</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:A14">
+    <cfRule type="duplicateValues" dxfId="12" priority="19"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17:A41">
-    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+  <conditionalFormatting sqref="A17:A45">
+    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A14">
-    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A41">
+  <conditionalFormatting sqref="A26:A45">
     <cfRule type="duplicateValues" dxfId="3" priority="3"/>
     <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>

--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\45087114\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2D3815B-E818-4BCD-92C0-1D93CE5BDE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089CAE42-1E27-A14B-9D99-E7D35AA69895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16020" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Documento</t>
   </si>
@@ -175,34 +175,13 @@
     <t>Carlos Emilio Riascos Angulo</t>
   </si>
   <si>
-    <t>Mirian Herrera Lucero</t>
-  </si>
-  <si>
-    <t>Betzy Danitza Medina Pereyra</t>
-  </si>
-  <si>
-    <t>08886630</t>
-  </si>
-  <si>
-    <t>Alexi John Mimbela Hinojosa</t>
-  </si>
-  <si>
-    <t>Gracia Cristina Alejandra Fernández Mejía</t>
-  </si>
-  <si>
-    <t>Cristina Medina Casapaico</t>
-  </si>
-  <si>
-    <t>07507292</t>
-  </si>
-  <si>
-    <t>Geraldine Consuelo Vargas Machuca Fajardo</t>
-  </si>
-  <si>
-    <t>Maria Cristina Palacios Ñuflo</t>
-  </si>
-  <si>
-    <t>Rosa Jazmin Vásquez Huaman</t>
+    <t>Carlos Ulises Hidalgo Arrieta</t>
+  </si>
+  <si>
+    <t>Milagros Velasquez Yahuacani</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ana Pilar Rosales Hermoza</t>
   </si>
 </sst>
 </file>
@@ -288,97 +267,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -839,14 +728,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -854,7 +743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1069832679</v>
       </c>
@@ -862,7 +751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1110538315</v>
       </c>
@@ -870,7 +759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1024591972</v>
       </c>
@@ -878,7 +767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1007719161</v>
       </c>
@@ -886,7 +775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>1022415180</v>
       </c>
@@ -894,7 +783,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>1007437362</v>
       </c>
@@ -902,7 +791,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>52360965</v>
       </c>
@@ -910,7 +799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>52359520</v>
       </c>
@@ -918,7 +807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>1033685058</v>
       </c>
@@ -926,7 +815,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>1043663400</v>
       </c>
@@ -934,7 +823,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>1064556081</v>
       </c>
@@ -942,7 +831,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>1024574799</v>
       </c>
@@ -950,7 +839,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>1023866590</v>
       </c>
@@ -958,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>1069750848</v>
       </c>
@@ -966,7 +855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>52937353</v>
       </c>
@@ -974,7 +863,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>33223712</v>
       </c>
@@ -982,7 +871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>1006854586</v>
       </c>
@@ -990,7 +879,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>1010207469</v>
       </c>
@@ -998,7 +887,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>1030678228</v>
       </c>
@@ -1006,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>1032677600</v>
       </c>
@@ -1014,7 +903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>1000784663</v>
       </c>
@@ -1022,7 +911,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>1006126137</v>
       </c>
@@ -1030,7 +919,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>1010231249</v>
       </c>
@@ -1038,7 +927,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>1022399552</v>
       </c>
@@ -1046,7 +935,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>1000873002</v>
       </c>
@@ -1054,7 +943,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>1128277446</v>
       </c>
@@ -1062,7 +951,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1000635646</v>
       </c>
@@ -1070,7 +959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1030680116</v>
       </c>
@@ -1078,7 +967,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1035230632</v>
       </c>
@@ -1086,7 +975,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1128450311</v>
       </c>
@@ -1094,7 +983,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>43482107</v>
       </c>
@@ -1102,7 +991,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>43182389</v>
       </c>
@@ -1110,7 +999,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>1035416124</v>
       </c>
@@ -1118,7 +1007,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>1096256836</v>
       </c>
@@ -1126,7 +1015,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>71311840</v>
       </c>
@@ -1134,7 +1023,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>1020103943</v>
       </c>
@@ -1142,7 +1031,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>1007253252</v>
       </c>
@@ -1150,7 +1039,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>1000406210</v>
       </c>
@@ -1158,7 +1047,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>1001138890</v>
       </c>
@@ -1166,7 +1055,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>1214729990</v>
       </c>
@@ -1174,7 +1063,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>1010213899</v>
       </c>
@@ -1182,7 +1071,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1232399996</v>
       </c>
@@ -1190,7 +1079,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>1001299432</v>
       </c>
@@ -1198,7 +1087,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>1006187617</v>
       </c>
@@ -1206,114 +1095,55 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>60399217</v>
+        <v>7215509</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>76566719</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>43067936</v>
-      </c>
-      <c r="B47" s="3" t="s">
+    <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>77377356</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>60856457</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>47096365</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>74712540</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>77338419</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A14">
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17:A53">
-    <cfRule type="duplicateValues" dxfId="13" priority="26"/>
+  <conditionalFormatting sqref="A17:A48">
+    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A53">
-    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+  <conditionalFormatting sqref="A26:A48">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:B38 A36:A37">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A46">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A48">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A49">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A50">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089CAE42-1E27-A14B-9D99-E7D35AA69895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AACC4E-CF74-9647-82AE-7684CA2C4110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16020" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Documento</t>
   </si>
@@ -182,6 +182,15 @@
   </si>
   <si>
     <t xml:space="preserve"> Ana Pilar Rosales Hermoza</t>
+  </si>
+  <si>
+    <t>Gracia Cristina Alejandra Fernandez</t>
+  </si>
+  <si>
+    <t>77337419</t>
+  </si>
+  <si>
+    <t>Rosa Jazmin Vasquez</t>
   </si>
 </sst>
 </file>
@@ -728,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -1117,6 +1126,22 @@
       </c>
       <c r="B48" s="3" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>60856457</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1134,10 +1159,10 @@
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17:A48">
+  <conditionalFormatting sqref="A17:A50">
     <cfRule type="duplicateValues" dxfId="4" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A48">
+  <conditionalFormatting sqref="A26:A50">
     <cfRule type="duplicateValues" dxfId="3" priority="3"/>
     <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
